--- a/results/Int Task Remove ACC 0.2/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.2/Linea_fi_all.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.022906197654941396 +/- 0.003972931328367863</t>
+          <t>0.022906197654941406 +/- 0.0039685149960464435</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0017587939698492483 +/- 0.0028016295952559087</t>
+          <t>0.0017169179229480803 +/- 0.0027868815966457096</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.00037688442211053497 +/- 0.0008259247455325002</t>
+          <t>-0.0003350083752093558 +/- 0.000812006676284143</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.0008375209380234283 +/- 0.0014138980750531078</t>
+          <t>-0.0008793969849246075 +/- 0.001468052608287955</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.04241922120961057 +/- 0.004964784843936578</t>
+          <t>0.042460646230323085 +/- 0.005002832367164669</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0497514498757249 +/- 0.005380311288472759</t>
+          <t>0.049668599834299866 +/- 0.0053962350574238895</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.03841392649903284 +/- 0.003438590693796973</t>
+          <t>0.03837524177949705 +/- 0.003402496468440395</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.05911025145067694 +/- 0.004447228739094763</t>
+          <t>0.05914893617021273 +/- 0.004486260102946152</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.0006189555125724833 +/- 0.0012257624385110116</t>
+          <t>0.0005802707930366968 +/- 0.0012141086906363762</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.043249516441005866 +/- 0.0026453107926156638</t>
+          <t>-0.04321083172147009 +/- 0.0026692456479690428</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.009623938536190845 +/- 0.0020995964392635917</t>
+          <t>0.009745248685806696 +/- 0.002247423086387422</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.017792155276991472 +/- 0.0035849834628874306</t>
+          <t>0.01771128184391424 +/- 0.0035886304459901053</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.1069551152446421 +/- 0.004940069439090441</t>
+          <t>0.10691467852810348 +/- 0.005002399383483112</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.06822716807367615 +/- 0.0047272029453367635</t>
+          <t>0.06826554105909441 +/- 0.004701121411189623</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.008557175748273183 +/- 0.0008758796784737915</t>
+          <t>-0.008672294704527983 +/- 0.0008950041281420392</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.0029546400332917224 +/- 0.002357388104580697</t>
+          <t>-0.0030378693300041615 +/- 0.00226446406332298</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.005534748231377451 +/- 0.0012900540990428717</t>
+          <t>-0.005493133583021226 +/- 0.0013000831753485988</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.005409904286308787 +/- 0.0014295101154654655</t>
+          <t>-0.005368289637952573 +/- 0.0014588887343285847</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0055987558320373275 +/- 0.002722728055989362</t>
+          <t>0.005559875583203732 +/- 0.0026714437614777393</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.00931871574001567 +/- 0.00497058764997912</t>
+          <t>-0.009279561472200482 +/- 0.005005165266098342</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.014369616288175392 +/- 0.003966193978746272</t>
+          <t>0.01444792482380578 +/- 0.004002362968849057</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.0010180109631949708 +/- 0.0016722127254551777</t>
+          <t>0.0010571652310101599 +/- 0.0016430802864806043</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.007830853563038387 +/- 0.004227935782832597</t>
+          <t>-0.007870007830853575 +/- 0.004137959660252592</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
